--- a/public/downloads/hw_test_plan_template.xlsx
+++ b/public/downloads/hw_test_plan_template.xlsx
@@ -706,14 +706,14 @@
     <row r="25" ht="18" customHeight="1">
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>峰值限流约 4.4A(typ) → 逐周期限流；严重短路进 hiccup 打嗝、自恢复</t>
+          <t>峰值限流 3.5–5.8A（min–max）→ 逐周期限流；严重短路进 hiccup 打嗝、自恢复</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>VIN UVLO 欠压锁定 ｜ 过温约 160℃ 关断带迟滞 ｜ SS 引脚外接电容设软启动</t>
+          <t>VIN UVLO 欠压锁定 ｜ 过温约 165℃ 关断带迟滞 ｜ SS 引脚外接电容设软启动</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="H24" s="13" t="inlineStr">
         <is>
-          <t>达约 4.4A(typ) 进逐周期限流；短路进 hiccup；解除后自恢复（查 datasheet）</t>
+          <t>达 3.5–5.8A 进逐周期限流；短路进 hiccup；解除后自恢复（查 datasheet）</t>
         </is>
       </c>
       <c r="I24" s="13" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>约 160℃ 关断、带迟滞恢复（查 datasheet）</t>
+          <t>约 165℃ 关断、带迟滞恢复（查 datasheet）</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>datasheet 限流约 4.4A + hiccup</t>
+          <t>datasheet 限流 3.5–5.8A + hiccup</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>达约4.4A(typ)进逐周期限流；短路进 hiccup 打嗝；解除后自恢复（查 datasheet）</t>
+          <t>达 3.5–5.8A 进逐周期限流；短路进 hiccup 打嗝；解除后自恢复（查 datasheet）</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>峰值限流约 4.4A + hiccup</t>
+          <t>峰值限流 3.5–5.8A + hiccup</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
@@ -3134,7 +3134,7 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>过温 OTP 约 160℃</t>
+          <t>过温 OTP 约 165℃</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
